--- a/_downloads/2f85416ced060b0b94d3009d4089a90a/Taller proyecto Café-Determinístico-CLASE.xlsx
+++ b/_downloads/2f85416ced060b0b94d3009d4089a90a/Taller proyecto Café-Determinístico-CLASE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\migue\Dropbox\ITM\ANÁLISIS DE RIESGOS\Talleres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CC8ECC-D408-4742-9C7A-03CF9261B107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08E2A6F-BE10-474A-8331-E8E1A37C1538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="751" activeTab="7" xr2:uid="{8BF2D7D1-9628-41D3-832C-45D8E5A38172}"/>
   </bookViews>
@@ -69,35 +69,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-El precio está por centados de dólar, pero al dividir por 1000 queda en dólar.</t>
+El precio está por centados de dólar, pero al dividir por 100 queda en dólar.</t>
         </r>
       </text>
     </comment>
     <comment ref="A35" authorId="0" shapeId="0" xr:uid="{28A43BF1-AE9C-435F-8651-BF13F37CEB32}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>MIGUEL JIMÉNEZ:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Se divide por 0,4536 para que quede en lb.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A37" authorId="0" shapeId="0" xr:uid="{4F32FF0E-AD49-4739-B697-9F1BD8595544}">
       <text>
         <r>
           <rPr>
@@ -473,9 +449,9 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
     <numFmt numFmtId="165" formatCode="####\-##"/>
     <numFmt numFmtId="166" formatCode="ddd\-dd\-mmm\-yy"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="[$USD]\ #,##0.000;[Red]\-[$USD]\ #,##0.000"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="[$USD]\ #,##0.000;[Red]\-[$USD]\ #,##0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="31" x14ac:knownFonts="1">
     <font>
@@ -1199,15 +1175,21 @@
     <xf numFmtId="8" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1281,12 +1263,6 @@
     </xf>
     <xf numFmtId="166" fontId="16" fillId="12" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -7459,12 +7435,12 @@
     <row r="2" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28"/>
       <c r="B2" s="29"/>
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="109"/>
       <c r="H2" s="1" t="s">
         <v>33</v>
       </c>
@@ -7472,22 +7448,22 @@
     <row r="3" spans="1:8" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
       <c r="B3" s="30"/>
-      <c r="C3" s="108" t="s">
+      <c r="C3" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="31"/>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="28"/>
@@ -29161,36 +29137,36 @@
     </row>
     <row r="2" spans="2:8" ht="27.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="49"/>
-      <c r="C2" s="111" t="s">
+      <c r="C2" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="115"/>
       <c r="H2" s="48" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50"/>
-      <c r="C3" s="114" t="s">
+      <c r="C3" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="116"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="118"/>
       <c r="H3" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="51"/>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="116"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="118"/>
     </row>
     <row r="5" spans="2:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="45"/>
@@ -31655,51 +31631,51 @@
     <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="29"/>
-      <c r="C2" s="117" t="s">
+      <c r="C2" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="119"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="121"/>
       <c r="M2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="30"/>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="122"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="124"/>
       <c r="M3" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="31"/>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="72" t="s">
@@ -31881,55 +31857,55 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="127"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="128" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="128"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="130"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="128" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="128"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="130"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -34345,7 +34321,7 @@
       <c r="C3" s="104">
         <v>11614</v>
       </c>
-      <c r="D3" s="129"/>
+      <c r="D3" s="105"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="77">
@@ -34357,7 +34333,7 @@
       <c r="C4" s="104">
         <v>11568</v>
       </c>
-      <c r="D4" s="129"/>
+      <c r="D4" s="105"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="77">
@@ -34369,7 +34345,7 @@
       <c r="C5" s="104">
         <v>11240</v>
       </c>
-      <c r="D5" s="129"/>
+      <c r="D5" s="105"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="77">
@@ -34381,7 +34357,7 @@
       <c r="C6" s="104">
         <v>11119</v>
       </c>
-      <c r="D6" s="129"/>
+      <c r="D6" s="105"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="77">
@@ -34393,7 +34369,7 @@
       <c r="C7" s="104">
         <v>12078</v>
       </c>
-      <c r="D7" s="129"/>
+      <c r="D7" s="105"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="77">
@@ -34405,7 +34381,7 @@
       <c r="C8" s="104">
         <v>12618</v>
       </c>
-      <c r="D8" s="129"/>
+      <c r="D8" s="105"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="77">
@@ -34417,7 +34393,7 @@
       <c r="C9" s="104">
         <v>11478</v>
       </c>
-      <c r="D9" s="129"/>
+      <c r="D9" s="105"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="77">
@@ -34429,7 +34405,7 @@
       <c r="C10" s="104">
         <v>7812</v>
       </c>
-      <c r="D10" s="129"/>
+      <c r="D10" s="105"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="77">
@@ -34441,7 +34417,7 @@
       <c r="C11" s="104">
         <v>8923</v>
       </c>
-      <c r="D11" s="129"/>
+      <c r="D11" s="105"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="77">
@@ -34453,7 +34429,7 @@
       <c r="C12" s="104">
         <v>7809</v>
       </c>
-      <c r="D12" s="129"/>
+      <c r="D12" s="105"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="77">
@@ -34465,7 +34441,7 @@
       <c r="C13" s="104">
         <v>7744</v>
       </c>
-      <c r="D13" s="129"/>
+      <c r="D13" s="105"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="77">
@@ -34477,7 +34453,7 @@
       <c r="C14" s="104">
         <v>10886</v>
       </c>
-      <c r="D14" s="129"/>
+      <c r="D14" s="105"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="77">
@@ -34489,7 +34465,7 @@
       <c r="C15" s="104">
         <v>12140</v>
       </c>
-      <c r="D15" s="129"/>
+      <c r="D15" s="105"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="77">
@@ -34501,7 +34477,7 @@
       <c r="C16" s="104">
         <v>14175</v>
       </c>
-      <c r="D16" s="129"/>
+      <c r="D16" s="105"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="77">
@@ -34513,7 +34489,7 @@
       <c r="C17" s="104">
         <v>14232</v>
       </c>
-      <c r="D17" s="129"/>
+      <c r="D17" s="105"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="77">
@@ -34525,7 +34501,7 @@
       <c r="C18" s="104">
         <v>14194</v>
       </c>
-      <c r="D18" s="129"/>
+      <c r="D18" s="105"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="77">
@@ -34537,7 +34513,7 @@
       <c r="C19" s="104">
         <v>13557</v>
       </c>
-      <c r="D19" s="129"/>
+      <c r="D19" s="105"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="77">
@@ -34549,7 +34525,7 @@
       <c r="C20" s="104">
         <v>14752</v>
       </c>
-      <c r="D20" s="129"/>
+      <c r="D20" s="105"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="77">
@@ -34561,13 +34537,13 @@
       <c r="C21" s="104">
         <v>13890</v>
       </c>
-      <c r="D21" s="129"/>
+      <c r="D21" s="105"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C22" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="130"/>
+      <c r="D22" s="106"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B30" s="86"/>
